--- a/reports/셀린느/history/2026-09-25/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-09-25/셀린느_league_mgf_report.xlsx
@@ -95,7 +95,7 @@
     <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중  문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
   </si>
   <si>
     <t>설익은체리</t>
@@ -251,7 +251,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>280경 3220조 6,404억 6,122만</t>
+    <t>280경 3220조 6404억 6122만</t>
   </si>
   <si>
     <t>2</t>
@@ -263,7 +263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>231경 7865조 5,718억 420만</t>
+    <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>186경 7071조 3,782억 8,079만</t>
+    <t>186경 7071조 3782억 8079만</t>
   </si>
   <si>
     <t>4</t>
@@ -299,7 +299,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>105경 4731조 5,416억 8,730만</t>
+    <t>105경 4731조 5416억 8730만</t>
   </si>
   <si>
     <t>5</t>
@@ -314,7 +314,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>85경 8894조 1,952억 8,378만</t>
+    <t>85경 8894조 1952억 8378만</t>
   </si>
   <si>
     <t>6</t>
@@ -326,7 +326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7,432억 2,421만</t>
+    <t>68경 6411조 7432억 2421만</t>
   </si>
   <si>
     <t>7</t>
@@ -338,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8,958억 6,847만</t>
+    <t>46경 1721조 8958억 6847만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>45경 5109조 8,480억 2,031만</t>
+    <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
     <t>9</t>
@@ -368,7 +368,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>43경 847조 2,572억 7,170만</t>
+    <t>43경 847조 2572억 7170만</t>
   </si>
   <si>
     <t>10</t>
@@ -380,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5,889억 4,039만</t>
+    <t>42경 3138조 5889억 4039만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,7 +398,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>29경 7613조 5,062억 2,329만</t>
+    <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 6216조 5,359억 3,679만</t>
+    <t>29경 6216조 5359억 3679만</t>
   </si>
   <si>
     <t>13</t>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>24경 3354조 9,527억 6,259만</t>
+    <t>24경 3354조 9527억 6259만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7,775억 656만</t>
+    <t>20경 5428조 7775억 656만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,7 +449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
   </si>
   <si>
-    <t>19경 7396조 2,622억 1,029만</t>
+    <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
     <t>16</t>
@@ -461,7 +461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9,521만</t>
+    <t>18경 9870조 503억 9521만</t>
   </si>
   <si>
     <t>17</t>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8,151억 3,649만</t>
+    <t>18경 5875조 8151억 3649만</t>
   </si>
   <si>
     <t>18</t>
@@ -488,7 +488,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1,960만</t>
+    <t>11경 2907조 6억 1960만</t>
   </si>
   <si>
     <t>19</t>
@@ -503,7 +503,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>9경 1574조 1,762억 1,736만</t>
+    <t>9경 1574조 1762억 1736만</t>
   </si>
   <si>
     <t>20</t>
@@ -530,7 +530,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>6경 5564조 1,888억 7,889만</t>
+    <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
     <t>22</t>
@@ -542,7 +542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4,474억 1,098만</t>
+    <t>6경 1783조 4474억 1098만</t>
   </si>
   <si>
     <t>23</t>
@@ -554,7 +554,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>5경 5478조 8,492억 3,032만</t>
+    <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
     <t>24</t>
@@ -572,7 +572,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>3경 4312조 1,092억 5,647만</t>
+    <t>3경 4312조 1092억 5647만</t>
   </si>
   <si>
     <t>25</t>
@@ -584,7 +584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1,885억 5,352만</t>
+    <t>3경 944조 1885억 5352만</t>
   </si>
   <si>
     <t>26</t>
@@ -596,7 +596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6,581억 7,894만</t>
+    <t>1경 5307조 6581억 7894만</t>
   </si>
   <si>
     <t>27</t>
@@ -608,7 +608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5301조 1,854억 5,754만</t>
+    <t>1경 5301조 1854억 5754만</t>
   </si>
   <si>
     <t>28</t>
@@ -623,7 +623,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>1경 4592조 3,595억 1,013만</t>
+    <t>1경 4592조 3595억 1013만</t>
   </si>
   <si>
     <t>29</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7,102억 6,148만</t>
+    <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -644,7 +644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>400경 7671조 206억 8,592만</t>
+    <t>400경 7671조 206억 8592만</t>
   </si>
   <si>
     <t>달하나별하나</t>
@@ -659,7 +659,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>278경 3626조 7,898억 1,199만</t>
+    <t>278경 3626조 7898억 1199만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
   </si>
   <si>
-    <t>178경 6628조 7,559억 4,369만</t>
+    <t>178경 6628조 7559억 4369만</t>
   </si>
   <si>
     <t>왕이된사나이</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>94경 871조 8,885억 5,305만</t>
+    <t>94경 871조 8885억 5305만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -689,7 +689,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>81경 393조 5,887억 8,702만</t>
+    <t>81경 393조 5887억 8702만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -698,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
   </si>
   <si>
-    <t>64경 6782조 2,788억 1,062만</t>
+    <t>64경 6782조 2788억 1062만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>41경 1905조 6,743억 903만</t>
+    <t>41경 1905조 6743억 903만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 9361조 9,717억 7,223만</t>
+    <t>22경 9361조 9717억 7223만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
   </si>
   <si>
-    <t>5경 9571조 1,335억 7,726만</t>
+    <t>5경 9571조 1335억 7726만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -734,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>4경 9304조 6,416억 3,411만</t>
+    <t>4경 9304조 6416억 3411만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -743,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 6299조 7,270억 8,249만</t>
+    <t>4경 6299조 7270억 8249만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -755,7 +755,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>4경 20조 8,028억 8,872만</t>
+    <t>4경 20조 8028억 8872만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -764,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>3경 4977조 1,514억 5,131만</t>
+    <t>3경 4977조 1514억 5131만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -773,7 +773,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 2289조 5,029억 5,012만</t>
+    <t>3경 2289조 5029억 5012만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -782,7 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 8524조 8,834억 6,295만</t>
+    <t>2경 8524조 8834억 6295만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -791,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
   </si>
   <si>
-    <t>2경 6335조 3,243억 7,245만</t>
+    <t>2경 6335조 3243억 7245만</t>
   </si>
   <si>
     <t>못함</t>
@@ -800,7 +800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 4177조 7,281억 3,707만</t>
+    <t>2경 4177조 7281억 3707만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -809,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 400조 2,278억 9,574만</t>
+    <t>2경 400조 2278억 9574만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -821,13 +821,13 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1경 9935조 5,126억 4,614만</t>
+    <t>1경 9935조 5126억 4614만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 8724조 1,000억 9,409만</t>
+    <t>1경 8724조 1000억 9409만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 7945조 2,053억 8,538만</t>
+    <t>1경 7945조 2053억 8538만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 3914조 4,654억 3,849만</t>
+    <t>1경 3914조 4654억 3849만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -854,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>1경 2959조 4,760억 5,668만</t>
+    <t>1경 2959조 4760억 5668만</t>
   </si>
   <si>
     <t>서두희</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 2438조 3,899억 3,059만</t>
+    <t>1경 2438조 3899억 3059만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1579조 6,334억 6,147만</t>
+    <t>1경 1579조 6334억 6147만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 837조 5,201억 2,986만</t>
+    <t>1경 837조 5201억 2986만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -893,7 +893,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9262조 3,412억 2,839만</t>
+    <t>9262조 3412억 2839만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -902,7 +902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>8854조 9,450억 4,226만</t>
+    <t>8854조 9450억 4226만</t>
   </si>
   <si>
     <t>김보들</t>
@@ -911,7 +911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
   </si>
   <si>
-    <t>5840조 7,231억 2,937만</t>
+    <t>5840조 7231억 2937만</t>
   </si>
   <si>
     <t>30</t>
@@ -926,7 +926,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5709조 6,081억 3,936만</t>
+    <t>5709조 6081억 3936만</t>
   </si>
   <si>
     <t>종리츄</t>
@@ -935,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1374경 9967조 4,966억 4,046만</t>
+    <t>1374경 9967조 4966억 4046만</t>
   </si>
   <si>
     <t>요쁘</t>
@@ -944,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
   </si>
   <si>
-    <t>146경 9210조 5,552억 2,224만</t>
+    <t>146경 9210조 5552억 2224만</t>
   </si>
   <si>
     <t>나야햄토리</t>
@@ -953,13 +953,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>90경 5508조 2,719억 5,514만</t>
+    <t>90경 5508조 2719억 5514만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>41경 6897조 9,928억 9,193만</t>
+    <t>41경 6897조 9928억 9193만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -968,7 +968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
   </si>
   <si>
-    <t>11경 1394조 5,468억 1,937만</t>
+    <t>11경 1394조 5468억 1937만</t>
   </si>
   <si>
     <t>독고사수</t>
@@ -977,7 +977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>10경 2197조 1,821억 9,825만</t>
+    <t>10경 2197조 1821억 9825만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -986,7 +986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>3경 1732조 6,831억 2,430만</t>
+    <t>3경 1732조 6831억 2430만</t>
   </si>
   <si>
     <t>정육츄</t>
@@ -998,7 +998,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2경 5047조 6,740억 1,185만</t>
+    <t>2경 5047조 6740억 1185만</t>
   </si>
   <si>
     <t>동작대교</t>
@@ -1007,7 +1007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
   </si>
   <si>
-    <t>1경 8332조 1,425억 2,718만</t>
+    <t>1경 8332조 1425억 2718만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1016,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 7475조 7,018억 3,841만</t>
+    <t>1경 7475조 7018억 3841만</t>
   </si>
   <si>
     <t>나야츄</t>
@@ -1025,7 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 1971조 6,929억 1,662만</t>
+    <t>1경 1971조 6929억 1662만</t>
   </si>
   <si>
     <t>날아라순자</t>
@@ -1037,7 +1037,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 54조 9,994억 7,226만</t>
+    <t>1경 54조 9994억 7226만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1046,7 +1046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>8199조 7,296억 9,107만</t>
+    <t>8199조 7296억 9107만</t>
   </si>
   <si>
     <t>꾸덕행</t>
@@ -1058,7 +1058,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>6827조 6,217억 3,831만</t>
+    <t>6827조 6217억 3831만</t>
   </si>
   <si>
     <t>lNOVAl</t>
@@ -1067,7 +1067,7 @@
     <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
   </si>
   <si>
-    <t>5566조 6,120억 2,581만</t>
+    <t>5566조 6120억 2581만</t>
   </si>
   <si>
     <t>천상츄</t>
@@ -1076,7 +1076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>5471조 457억 5,918만</t>
+    <t>5471조 457억 5918만</t>
   </si>
   <si>
     <t>넹또</t>
@@ -1085,7 +1085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
   </si>
   <si>
-    <t>5145조 1,415억 4,710만</t>
+    <t>5145조 1415억 4710만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1094,7 +1094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>5001조 9,074억 5,704만</t>
+    <t>5001조 9074억 5704만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1103,7 +1103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>4302조 3,804억 7,260만</t>
+    <t>4302조 3804억 7260만</t>
   </si>
   <si>
     <t>직만</t>
@@ -1112,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>4197조 2,196억 4,458만</t>
+    <t>4197조 2196억 4458만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>3413조 2,055억 7,746만</t>
+    <t>3413조 2055억 7746만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1133,7 +1133,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>3272조 1,723억 9,516만</t>
+    <t>3272조 1723억 9516만</t>
   </si>
   <si>
     <t>나야김대장</t>
@@ -1142,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>3199조 8,996억 1,901만</t>
+    <t>3199조 8996억 1901만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1151,7 +1151,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>3199조 3,306억 4,775만</t>
+    <t>3199조 3306억 4775만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1160,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
-    <t>2827조 6,717억 8,583만</t>
+    <t>2827조 6717억 8583만</t>
   </si>
   <si>
     <t>포이즈</t>
@@ -1169,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
   </si>
   <si>
-    <t>2692조 8,173억 3,981만</t>
+    <t>2692조 8173억 3981만</t>
   </si>
   <si>
     <t>푸들츄</t>
@@ -1178,7 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>2632조 6,912억 5,153만</t>
+    <t>2632조 6912억 5153만</t>
   </si>
   <si>
     <t>궁금증유발</t>
@@ -1187,7 +1187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
   </si>
   <si>
-    <t>2280조 94억 3,832만</t>
+    <t>2280조 94억 3832만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -1196,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>2064조 1,071억 8,482만</t>
+    <t>2064조 1071억 8482만</t>
   </si>
   <si>
     <t>산과바다</t>
@@ -1205,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1652조 9,566억 8,362만</t>
+    <t>1652조 9566억 8362만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 4823조 3,360억 295만</t>
+    <t>25경 4823조 3360억 295만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5,082억 5,270만</t>
+    <t>19경 8464조 5082억 5270만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -1232,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3,052억 4,003만</t>
+    <t>12경 4306조 3052억 4003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1241,7 +1241,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7,960억 279만</t>
+    <t>11경 4105조 7960억 279만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>10경 6154조 8799억 4676만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1250,16 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>10경 4738조 815억 6,221만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>10경 3451조 2,235억 7,402만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1268,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3290조 8,758억 715만</t>
+    <t>9경 3423조 3510억 8891만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -1277,7 +1277,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2,651억 9,696만</t>
+    <t>7경 6148조 2651억 9696만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1286,16 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>7경 3059조 933억 2,511만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>6경 7083조 325억 1,634만</t>
+    <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1304,7 +1304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9,003억 4,099만</t>
+    <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1313,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4,834억 827만</t>
+    <t>2경 4504조 4834억 827만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -1322,7 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 4130조 5,641억 7,043만</t>
+    <t>2경 4130조 5641억 7043만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -1331,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2,021억 502만</t>
+    <t>2경 3271조 2021억 502만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1340,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
   </si>
   <si>
-    <t>2경 2936조 4,015억 1,704만</t>
+    <t>2경 2936조 4015억 1704만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1349,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 1323조 7,490억 7,475만</t>
+    <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -1358,13 +1358,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3,650억 1,564만</t>
+    <t>1경 9258조 3650억 1564만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5,691억 7,924만</t>
+    <t>1경 7139조 5691억 7924만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -1373,7 +1373,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1,968억 392만</t>
+    <t>1경 5876조 1968억 392만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -1382,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 5688조 4,374억 8,127만</t>
+    <t>1경 5688조 4374억 8127만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1391,7 +1391,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5,412억 6,446만</t>
+    <t>1경 3148조 5412억 6446만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -1400,7 +1400,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 2312조 9,961억 3,717만</t>
+    <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
     <t>라똥삐</t>
@@ -1409,7 +1409,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
   </si>
   <si>
-    <t>1경 2085조 1,284억 3,396만</t>
+    <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -1418,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
   </si>
   <si>
-    <t>1경 1856조 4,618억 6,137만</t>
+    <t>1경 1856조 4618억 6137만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -1427,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2,945억 9,039만</t>
+    <t>1경 2945억 9039만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1436,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2,165억 2,470만</t>
+    <t>6443조 2165억 2470만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -1445,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3,675억 8,873만</t>
+    <t>5796조 3675억 8873만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -1454,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>341조 6,408억 9,657만</t>
+    <t>341조 6408억 9657만</t>
   </si>
   <si>
     <t>베르카암프</t>
@@ -1466,7 +1466,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>528조 2,903억 8,564만</t>
+    <t>528조 2903억 8564만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1478,7 +1478,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>510조 8,522억 3,023만</t>
+    <t>510조 8522억 3023만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1487,7 +1487,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>485조 6,946억 3,853만</t>
+    <t>485조 6946억 3853만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1496,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>462조 6,492억 9,502만</t>
+    <t>462조 6492억 9502만</t>
   </si>
   <si>
     <t>썬콜원준띠</t>
@@ -1505,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
   </si>
   <si>
-    <t>404조 5,216억 8,702만</t>
+    <t>404조 5216억 8702만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1514,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
   </si>
   <si>
-    <t>358조 5,526억 3,562만</t>
+    <t>358조 5526억 3562만</t>
   </si>
   <si>
     <t>말랑랑말이</t>
@@ -1523,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>319조 6,634억 9,916만</t>
+    <t>319조 6634억 9916만</t>
   </si>
   <si>
     <t>날씬</t>
@@ -1532,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>281조 8,365억 8,619만</t>
+    <t>281조 8365억 8619만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1544,7 +1544,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>250조 8,464억 5,632만</t>
+    <t>250조 8464억 5632만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1553,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
   </si>
   <si>
-    <t>185조 2,853억 5,484만</t>
+    <t>185조 2853억 5484만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1565,7 +1565,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>183조 8,405억 4,218만</t>
+    <t>183조 8405억 4218만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>166조 3,857억 4,091만</t>
+    <t>166조 3857억 4091만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1586,7 +1586,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>154조 7,346억 1,516만</t>
+    <t>154조 7346억 1516만</t>
   </si>
   <si>
     <t>멍뭉이다</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%AD%89%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>153조 5,425억 984만</t>
+    <t>153조 5425억 984만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1604,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>138조 6,113억 1,862만</t>
+    <t>138조 6113억 1862만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>134조 4,998억 5,770만</t>
+    <t>134조 4998억 5770만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>130조 5,440억 9,674만</t>
+    <t>130조 5440억 9674만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>128조 1,033억 8,744만</t>
+    <t>128조 1033억 8744만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>97조 5,494억 6,110만</t>
+    <t>97조 5494억 6110만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>82조 5,120억 1,455만</t>
+    <t>82조 5120억 1455만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1661,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>55조 296억 2,286만</t>
+    <t>55조 296억 2286만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1670,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>31조 9,560억 6,444만</t>
+    <t>31조 9560억 6444만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1679,7 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>20조 8,845억 2,964만</t>
+    <t>20조 8845억 2964만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1691,7 +1691,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>14조 6,666억 5,274만</t>
+    <t>14조 6666억 5274만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1703,7 +1703,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>12조 8,251억 2,721만</t>
+    <t>12조 8251억 2721만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1712,13 +1712,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A0%9C%EB%AA%85%ED%99%95%EC%B0%A2</t>
   </si>
   <si>
-    <t>10조 9,536억 4,351만</t>
+    <t>10조 9536억 4351만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>6조 4,425억 8,179만</t>
+    <t>6조 4425억 8179만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1730,7 +1730,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 4,360억 4,592만</t>
+    <t>2조 4360억 4592만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1745,7 +1745,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1,456억 5,188만</t>
+    <t>1456억 5188만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1760,7 +1760,7 @@
     <t>82</t>
   </si>
   <si>
-    <t>112억 5,433만</t>
+    <t>112억 5433만</t>
   </si>
 </sst>
 </file>
@@ -2134,7 +2134,7 @@
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" customWidth="1"/>
-    <col min="11" max="11" width="48.7109375" customWidth="1"/>
+    <col min="11" max="11" width="47.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2407,7 +2407,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3419,7 +3419,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4464,7 +4464,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5509,7 +5509,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5693,7 +5693,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>112</v>
@@ -5725,7 +5725,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>112</v>
@@ -5821,10 +5821,10 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>419</v>
@@ -5853,10 +5853,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>422</v>
@@ -6488,7 +6488,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
